--- a/data/trans_orig/IQ21C-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ21C-Habitat-trans_orig.xlsx
@@ -2588,7 +2588,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1974</t>
+          <t>2083</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>83,68%</t>
         </is>
       </c>
     </row>
@@ -6935,7 +6935,7 @@
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>3315</t>
+          <t>3316</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -6950,7 +6950,7 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>50,71%</t>
         </is>
       </c>
     </row>
@@ -7152,12 +7152,12 @@
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>650</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>4539</t>
+          <t>4165</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -7167,12 +7167,12 @@
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>63,71%</t>
         </is>
       </c>
     </row>
@@ -7268,7 +7268,7 @@
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>3355</t>
+          <t>3507</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -7283,7 +7283,7 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>51,32%</t>
+          <t>53,64%</t>
         </is>
       </c>
     </row>
@@ -7379,7 +7379,7 @@
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>3154</t>
+          <t>2515</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -7394,7 +7394,7 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>38,47%</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>3210</t>
+          <t>3230</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -7505,7 +7505,7 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>49,4%</t>
         </is>
       </c>
     </row>
@@ -7601,7 +7601,7 @@
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>2950</t>
+          <t>3388</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -7616,7 +7616,7 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>51,82%</t>
         </is>
       </c>
     </row>
@@ -7712,7 +7712,7 @@
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>2650</t>
+          <t>2622</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>40,1%</t>
         </is>
       </c>
     </row>
@@ -10176,7 +10176,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>2636</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10191,7 +10191,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>80,23%</t>
         </is>
       </c>
     </row>
@@ -10398,7 +10398,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2587</t>
+          <t>2612</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10413,7 +10413,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>79,48%</t>
         </is>
       </c>
     </row>
@@ -10731,7 +10731,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2620</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10746,7 +10746,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>79,74%</t>
+          <t>79,41%</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2670</t>
+          <t>2665</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>81,11%</t>
         </is>
       </c>
     </row>
@@ -13074,7 +13074,7 @@
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>3051</t>
+          <t>2484</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -13089,7 +13089,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>68,21%</t>
         </is>
       </c>
     </row>
@@ -13185,7 +13185,7 @@
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>2911</t>
+          <t>2905</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -13200,7 +13200,7 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>79,79%</t>
         </is>
       </c>
     </row>
@@ -13851,7 +13851,7 @@
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>2985</t>
+          <t>2972</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -13866,7 +13866,7 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>81,98%</t>
+          <t>81,64%</t>
         </is>
       </c>
     </row>
@@ -14044,7 +14044,7 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>2692</t>
+          <t>3236</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -14059,7 +14059,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>45,98%</t>
+          <t>55,27%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -14079,7 +14079,7 @@
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>2718</t>
+          <t>2702</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -14094,7 +14094,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,45%</t>
         </is>
       </c>
     </row>
@@ -14155,7 +14155,7 @@
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2445</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -14170,7 +14170,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -14190,7 +14190,7 @@
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>2482</t>
+          <t>2468</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -14205,7 +14205,7 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>25,98%</t>
         </is>
       </c>
     </row>
@@ -14453,7 +14453,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>3009</t>
+          <t>3101</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -14488,7 +14488,7 @@
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>2680</t>
+          <t>3297</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -14503,7 +14503,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -14523,7 +14523,7 @@
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>4370</t>
+          <t>4700</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -14538,7 +14538,7 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>49,48%</t>
         </is>
       </c>
     </row>
@@ -14594,12 +14594,12 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>644</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>3949</t>
+          <t>4013</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -14609,12 +14609,12 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>67,44%</t>
+          <t>68,53%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -14629,12 +14629,12 @@
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>632</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>4783</t>
+          <t>4705</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -14644,12 +14644,12 @@
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>50,36%</t>
+          <t>49,53%</t>
         </is>
       </c>
     </row>
@@ -14710,7 +14710,7 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2622</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -14725,7 +14725,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>44,79%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -14745,7 +14745,7 @@
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>2732</t>
+          <t>2614</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -14760,7 +14760,7 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>27,52%</t>
         </is>
       </c>
     </row>
@@ -15008,7 +15008,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>2843</t>
+          <t>2836</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -15023,7 +15023,7 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>78,03%</t>
+          <t>77,86%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -15043,7 +15043,7 @@
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>2624</t>
+          <t>2686</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -15058,7 +15058,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>45,88%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -15078,7 +15078,7 @@
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>3784</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -15093,7 +15093,7 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>38,46%</t>
         </is>
       </c>
     </row>
@@ -15119,7 +15119,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>2936</t>
+          <t>2943</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -15189,7 +15189,7 @@
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>4060</t>
+          <t>4022</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
@@ -15204,7 +15204,7 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>42,35%</t>
         </is>
       </c>
     </row>
@@ -15230,7 +15230,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>2570</t>
+          <t>2772</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -15245,7 +15245,7 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -15265,7 +15265,7 @@
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>2671</t>
+          <t>2669</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -15280,7 +15280,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>45,58%</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -15300,7 +15300,7 @@
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>4163</t>
+          <t>4132</t>
         </is>
       </c>
       <c r="U67" s="2" t="inlineStr">
@@ -15315,7 +15315,7 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>43,5%</t>
         </is>
       </c>
     </row>
@@ -17431,7 +17431,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2752</t>
+          <t>2670</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -17446,7 +17446,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>79,36%</t>
         </is>
       </c>
     </row>
@@ -17472,7 +17472,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1987</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -17487,7 +17487,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -17542,7 +17542,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2559</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -17557,7 +17557,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>81,85%</t>
         </is>
       </c>
     </row>
@@ -18097,7 +18097,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2602</t>
+          <t>2484</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -18112,7 +18112,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>77,36%</t>
+          <t>73,84%</t>
         </is>
       </c>
     </row>
@@ -18319,7 +18319,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2626</t>
+          <t>2750</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -18334,7 +18334,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>78,07%</t>
+          <t>81,74%</t>
         </is>
       </c>
     </row>
@@ -21632,7 +21632,7 @@
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>3180</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -21647,7 +21647,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -21667,7 +21667,7 @@
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>3489</t>
+          <t>4198</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -21682,7 +21682,7 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>45,77%</t>
         </is>
       </c>
     </row>
@@ -21708,7 +21708,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>3021</t>
+          <t>2989</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -21723,7 +21723,7 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>62,58%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -21778,7 +21778,7 @@
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>3142</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -21793,7 +21793,7 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>39,83%</t>
         </is>
       </c>
     </row>
@@ -21819,7 +21819,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>2663</t>
+          <t>2607</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -21834,7 +21834,7 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>55,75%</t>
+          <t>54,57%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -21889,7 +21889,7 @@
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>3226</t>
+          <t>2617</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -21904,7 +21904,7 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>28,54%</t>
         </is>
       </c>
     </row>
@@ -21965,7 +21965,7 @@
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>3018</t>
+          <t>2939</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -21980,7 +21980,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>68,69%</t>
+          <t>66,9%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -22000,7 +22000,7 @@
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>3838</t>
+          <t>3726</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -22015,7 +22015,7 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>40,63%</t>
         </is>
       </c>
     </row>
@@ -22041,7 +22041,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>3208</t>
+          <t>3195</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -22056,7 +22056,7 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>67,16%</t>
+          <t>66,87%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -22111,7 +22111,7 @@
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>3628</t>
+          <t>3822</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -22126,7 +22126,7 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>41,67%</t>
         </is>
       </c>
     </row>
@@ -22374,7 +22374,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>2442</t>
+          <t>2517</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -22389,7 +22389,7 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>52,69%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -22409,7 +22409,7 @@
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>2799</t>
+          <t>2818</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -22424,7 +22424,7 @@
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>64,13%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -22444,7 +22444,7 @@
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>3555</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -22459,7 +22459,7 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>38,76%</t>
         </is>
       </c>
     </row>
@@ -22485,7 +22485,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>2896</t>
+          <t>2632</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -22500,7 +22500,7 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>60,63%</t>
+          <t>55,09%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -22555,7 +22555,7 @@
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>3327</t>
+          <t>2894</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -22570,7 +22570,7 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>31,56%</t>
         </is>
       </c>
     </row>
@@ -22596,7 +22596,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>3446</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -22611,7 +22611,7 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>71,3%</t>
+          <t>72,14%</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -22631,7 +22631,7 @@
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>3469</t>
+          <t>3382</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -22646,7 +22646,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>76,96%</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -22661,12 +22661,12 @@
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>697</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>5419</t>
+          <t>5528</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
@@ -22676,12 +22676,12 @@
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>59,09%</t>
+          <t>60,28%</t>
         </is>
       </c>
     </row>
@@ -22742,7 +22742,7 @@
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>3216</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -22757,7 +22757,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>70,59%</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -22777,7 +22777,7 @@
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>3746</t>
+          <t>3845</t>
         </is>
       </c>
       <c r="U67" s="2" t="inlineStr">
@@ -22792,7 +22792,7 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>41,93%</t>
         </is>
       </c>
     </row>
@@ -30143,7 +30143,7 @@
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>3442</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
@@ -30158,7 +30158,7 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>85,95%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ21C-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ21C-Habitat-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -646,419 +651,203 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>5,0</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>6,0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3,92</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,0</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>6,0</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>3,22</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>6,0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3,92</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>6,0</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>3.917631502354466</v>
+      </c>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="5" t="inlineStr"/>
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>3.21973207708329</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>3.917631502354466</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1,0; 7,0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>1,0; 5,0</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>1,0; 7,0</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr"/>
+      <c r="D5" s="5" t="inlineStr"/>
+      <c r="E5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="5" t="inlineStr"/>
+      <c r="G5" s="5" t="inlineStr"/>
+      <c r="H5" s="5" t="inlineStr"/>
+      <c r="I5" s="5" t="inlineStr"/>
+      <c r="J5" s="5" t="inlineStr"/>
+      <c r="K5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" s="5" t="inlineStr"/>
+      <c r="M5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="N6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>9,08</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>6,04</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>3,0</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,32</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>9,01</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>6,2</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>3,19</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>6,89</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>6,0; 12,0</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>5,0; 7,0</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,0; 2,0</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,88; 16,74</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>3,51; 10,56</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1,2; 5,75</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>1,06; 14,59</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+      <c r="C7" s="5" t="n">
+        <v>9.084714583510795</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>6.03878038428134</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5" t="inlineStr"/>
+      <c r="G7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>1.324901691057029</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>9.009058409217731</v>
+      </c>
+      <c r="J7" s="5" t="inlineStr"/>
+      <c r="K7" s="5" t="n">
+        <v>6.198697380576871</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>3.1899594047888</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>6.894459524887757</v>
+      </c>
+      <c r="N7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>6,0</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>20,54</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>15,24</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1,99</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>6,0</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>20,54</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>15,24</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>1,99</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" s="5" t="inlineStr"/>
+      <c r="F8" s="5" t="inlineStr"/>
+      <c r="G8" s="5" t="inlineStr"/>
+      <c r="H8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>1.884458957925876</v>
+      </c>
+      <c r="J8" s="5" t="inlineStr"/>
+      <c r="K8" s="5" t="n">
+        <v>3.50798019971896</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>1.195867771163442</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>1.060790532035343</v>
+      </c>
+      <c r="N8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>2,0; 32,31</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>1,0; 24,0</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>1,0; 3,0</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>2,0; 32,31</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>1,0; 24,0</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>1,0; 3,0</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E9" s="5" t="inlineStr"/>
+      <c r="F9" s="5" t="inlineStr"/>
+      <c r="G9" s="5" t="inlineStr"/>
+      <c r="H9" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>16.74253567923604</v>
+      </c>
+      <c r="J9" s="5" t="inlineStr"/>
+      <c r="K9" s="5" t="n">
+        <v>10.56265135703023</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>5.748839311511236</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>14.58782215488367</v>
+      </c>
+      <c r="N9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1066,277 +855,359 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>2,93</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>3,98</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3,0</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2,09</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>6,0</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,9</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3,12</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>4,01</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>3,94</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3,09</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,09</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>20.53640549073584</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>15.23766768359364</v>
+      </c>
+      <c r="F10" s="5" t="inlineStr"/>
+      <c r="G10" s="5" t="inlineStr"/>
+      <c r="H10" s="5" t="inlineStr"/>
+      <c r="I10" s="5" t="inlineStr"/>
+      <c r="J10" s="5" t="n">
+        <v>1.994133568450174</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>20.53640549073584</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>15.23766768359364</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>1.994133568450174</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>2,0; 4,0</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 6,0</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1,0; 3,0</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 7,0</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>1,33; 6,0</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>2,0; 6,0</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>1,1; 6,48</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>1,5; 5,34</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>1,0; 3,0</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr"/>
+      <c r="D11" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="5" t="inlineStr"/>
+      <c r="H11" s="5" t="inlineStr"/>
+      <c r="I11" s="5" t="inlineStr"/>
+      <c r="J11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" s="5" t="inlineStr"/>
+      <c r="L11" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr"/>
+      <c r="D12" s="5" t="n">
+        <v>32.31262682223398</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="5" t="inlineStr"/>
+      <c r="H12" s="5" t="inlineStr"/>
+      <c r="I12" s="5" t="inlineStr"/>
+      <c r="J12" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K12" s="5" t="inlineStr"/>
+      <c r="L12" s="5" t="n">
+        <v>32.31262682223398</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>2.934909301702958</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>3.982313809677734</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>2.092094372359923</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>3.899461829655414</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>3.117608586856892</v>
+      </c>
+      <c r="J13" s="5" t="inlineStr"/>
+      <c r="K13" s="5" t="n">
+        <v>4.011872382975575</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>3.944608662086914</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>3.090178856760574</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>2.092094372359923</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="5" t="inlineStr"/>
+      <c r="F14" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="5" t="inlineStr"/>
+      <c r="H14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="J14" s="5" t="inlineStr"/>
+      <c r="K14" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>1.101719041034862</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr"/>
+      <c r="F15" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G15" s="5" t="inlineStr"/>
+      <c r="H15" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="J15" s="5" t="inlineStr"/>
+      <c r="K15" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>6.484766955255057</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>5.339992240209508</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>5,82</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>10,01</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>6,78</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2,09</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>3,4</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2,5</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>6,29</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>3,06</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>4,91</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>7,13</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>6,53</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>2,66</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>3,98; 9,02</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>4,57; 20,73</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1,6; 17,21</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>1,0; 3,0</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1,95; 5,41</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,76; 5,84</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,76; 12,67</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1,0; 6,0</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3,41; 7,05</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>3,69; 15,33</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3,16; 12,4</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,43; 4,55</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>5.824528216749528</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>10.0117040549995</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>6.783487962433942</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>2.092094372359923</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>3.398623865093191</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>2.495939656690903</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>6.292742909907888</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>3.059347354425384</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>4.908291560630805</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>7.128775094834062</v>
+      </c>
+      <c r="M16" s="5" t="n">
+        <v>6.527851752043035</v>
+      </c>
+      <c r="N16" s="5" t="n">
+        <v>2.663058864150678</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>3.977352589402717</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>4.570030226804024</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>1.603195711487401</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>1.95490851016897</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>0.7618187334008142</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>2.756447992739487</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>3.409575231663201</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>3.693502352574127</v>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>3.159197175522068</v>
+      </c>
+      <c r="N17" s="5" t="n">
+        <v>1.433746933250949</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>9.015038195071281</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>20.73114564541212</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>17.20635381634974</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>5.406845633220053</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>5.839270523905964</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>12.67180237597286</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>6.000000000000001</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>7.047702658696782</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>15.33327834137176</v>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>12.39896215667485</v>
+      </c>
+      <c r="N18" s="5" t="n">
+        <v>4.552402015695894</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1344,15 +1215,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
     <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
